--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -64,7 +64,14 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="2">
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -89,8 +89,38 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFDEB887"/>
-        <x:bgColor rgb="FFDEB887"/>
+        <x:fgColor rgb="FF90EE90"/>
+        <x:bgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9967A"/>
+        <x:bgColor rgb="FFE9967A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF1493"/>
+        <x:bgColor rgb="FFFF1493"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF00CED1"/>
+        <x:bgColor rgb="FF00CED1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1E90FF"/>
+        <x:bgColor rgb="FF1E90FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA9A9A9"/>
+        <x:bgColor rgb="FFA9A9A9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -101,38 +131,8 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA9A9A9"/>
-        <x:bgColor rgb="FFA9A9A9"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1E90FF"/>
-        <x:bgColor rgb="FF1E90FF"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF00CED1"/>
-        <x:bgColor rgb="FF00CED1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFF1493"/>
-        <x:bgColor rgb="FFFF1493"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE9967A"/>
-        <x:bgColor rgb="FFE9967A"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-        <x:bgColor rgb="FF90EE90"/>
+        <x:fgColor rgb="FFDEB887"/>
+        <x:bgColor rgb="FFDEB887"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -183,40 +183,40 @@
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="46" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="46" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="14" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="7" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="7" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -257,7 +257,27 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="46" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -265,43 +285,23 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="14" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -618,82 +618,82 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="A2" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="A3" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="A4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="s">
+      <x:c r="A5" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s"/>
+      <x:c r="A6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s"/>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="A7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s"/>
+      <x:c r="A7" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s"/>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="7" t="s"/>
-      <x:c r="B8" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
+      <x:c r="A8" s="2" t="s"/>
+      <x:c r="B8" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
-      <x:c r="A9" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B9" s="8" t="s"/>
-      <x:c r="C9" s="8" t="s">
+      <x:c r="A9" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s"/>
+      <x:c r="C9" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -715,82 +715,82 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="s"/>
+      <x:c r="A1" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s"/>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
+      <x:c r="A2" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="A3" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
+      <x:c r="A4" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s"/>
+      <x:c r="A5" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="s"/>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
+      <x:c r="A6" s="2" t="s"/>
+      <x:c r="B6" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="A7" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="A7" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B8" s="8" t="s"/>
-      <x:c r="C8" s="8" t="s">
+      <x:c r="A8" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s"/>
+      <x:c r="C8" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -812,40 +812,40 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="5" t="s">
+      <x:c r="A2" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="8" t="s">
+      <x:c r="A3" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="4" t="s">
+      <x:c r="A4" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="2" t="s">
+      <x:c r="A5" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="6" t="s">
+      <x:c r="A6" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="6" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -865,40 +865,40 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="6" t="s">
+      <x:c r="A1" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="8" t="s">
+      <x:c r="A2" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="4" t="s">
+      <x:c r="A3" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="2" t="s">
+      <x:c r="A4" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="1" t="s">
+      <x:c r="A5" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="5" t="s">
+      <x:c r="A6" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="2" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -918,22 +918,22 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B1" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C1" s="8" t="s"/>
+      <x:c r="A1" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s"/>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="5" t="s"/>
+      <x:c r="A2" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -956,64 +956,64 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
-      <x:c r="A1" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="s">
+      <x:c r="A1" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
-      <x:c r="A2" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="5" t="s">
+      <x:c r="A2" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
-      <x:c r="A3" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="A3" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
+      <x:c r="A4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
-      <x:c r="A5" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
+      <x:c r="A5" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
-      <x:c r="A6" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="s">
+      <x:c r="A6" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
-      <x:c r="A7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="s">
+      <x:c r="A7" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
-      <x:c r="A8" s="7" t="s"/>
-      <x:c r="B8" s="8" t="s"/>
+      <x:c r="A8" s="2" t="s"/>
+      <x:c r="B8" s="1" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1043,7 +1043,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="5" t="n">
+      <x:c r="A3" s="4" t="n">
         <x:v>1.15</x:v>
       </x:c>
     </x:row>
@@ -1058,15 +1058,15 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="4" t="n">
+      <x:c r="A6" s="5" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="2" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1086,40 +1086,40 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="5" t="n">
+      <x:c r="A1" s="4" t="n">
         <x:v>1.15</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="8" t="n">
+      <x:c r="A2" s="1" t="n">
         <x:v>1.3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="6" t="n">
+      <x:c r="A3" s="3" t="n">
         <x:v>4.15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="2" t="n">
+      <x:c r="A4" s="7" t="n">
         <x:v>4.3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="4" t="n">
+      <x:c r="A5" s="5" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="1" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>1230</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="6" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1169,10 +1169,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="2" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1222,10 +1222,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="6" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1245,82 +1245,82 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="7" t="s"/>
-      <x:c r="B1" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C1" s="7" t="s">
+      <x:c r="A1" s="2" t="s"/>
+      <x:c r="B1" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="A2" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="A3" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="A4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="s">
+      <x:c r="A5" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s"/>
+      <x:c r="A6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s"/>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="A7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s"/>
+      <x:c r="A7" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s"/>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B8" s="8" t="s"/>
-      <x:c r="C8" s="8" t="s">
+      <x:c r="A8" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s"/>
+      <x:c r="C8" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1342,38 +1342,38 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="7" t="s"/>
+      <x:c r="A1" s="2" t="s"/>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="3" t="s"/>
+      <x:c r="A2" s="6" t="s"/>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="1" t="s">
+      <x:c r="A3" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="5" t="s">
+      <x:c r="A4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="4" t="s">
+      <x:c r="A5" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="8" t="s">
+      <x:c r="A6" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="2" t="s">
+      <x:c r="A7" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="6" t="s">
+      <x:c r="A8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1395,40 +1395,40 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="6" t="s">
+      <x:c r="A1" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="8" t="s">
+      <x:c r="A2" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="4" t="s">
+      <x:c r="A4" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="5" t="s">
+      <x:c r="A5" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="1" t="s">
+      <x:c r="A6" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="6" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1448,82 +1448,82 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="A1" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C1" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
+      <x:c r="A2" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="A3" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="A4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s"/>
+      <x:c r="A5" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="s"/>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s"/>
+      <x:c r="A6" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s"/>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="A7" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s">
+      <x:c r="A7" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s"/>
+      <x:c r="C7" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="7" t="s"/>
-      <x:c r="B8" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
+      <x:c r="A8" s="2" t="s"/>
+      <x:c r="B8" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1545,40 +1545,40 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="5" t="s">
+      <x:c r="A2" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="4" t="s">
+      <x:c r="A3" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="8" t="s">
+      <x:c r="A4" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="2" t="s">
+      <x:c r="A5" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="6" t="s">
+      <x:c r="A6" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="2" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1598,40 +1598,40 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="6" t="s">
+      <x:c r="A1" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="8" t="s">
+      <x:c r="A2" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="4" t="s">
+      <x:c r="A4" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="5" t="s">
+      <x:c r="A5" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="1" t="s">
+      <x:c r="A6" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2" t="s"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="6" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1651,82 +1651,82 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
+      <x:c r="A1" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C1" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
+      <x:c r="A2" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="A3" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s"/>
+      <x:c r="A4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s"/>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="A5" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s"/>
+      <x:c r="A6" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s"/>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="A7" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s">
+      <x:c r="A7" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s"/>
+      <x:c r="C7" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="7" t="s"/>
-      <x:c r="B8" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
+      <x:c r="A8" s="2" t="s"/>
+      <x:c r="B8" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1748,82 +1748,82 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="s"/>
+      <x:c r="A1" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s"/>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="s"/>
-      <x:c r="C2" s="8" t="s">
+      <x:c r="A2" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="A3" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
+      <x:c r="A4" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="s">
+      <x:c r="A5" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="s">
+      <x:c r="A6" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="A7" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s"/>
+      <x:c r="A7" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s"/>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="7" t="s"/>
-      <x:c r="B8" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
+      <x:c r="A8" s="2" t="s"/>
+      <x:c r="B8" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -156,152 +156,152 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="21">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="8" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="9" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="6" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="8" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="9" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="21">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
